--- a/COLLARES SWA.xlsx
+++ b/COLLARES SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9F8753-602B-4CFE-976E-C5B8842A9BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A636A673-8C85-4281-BAFA-BE356296C673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{858CB977-914C-4BFC-86E4-E9C9E95983A5}"/>
   </bookViews>
@@ -120,7 +120,7 @@
     <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="166" formatCode="_-[$Q-100A]* #,##0.00_-;\-[$Q-100A]* #,##0.00_-;_-[$Q-100A]* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +148,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -205,10 +212,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -245,8 +253,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -268,13 +280,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>1143000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -311,13 +323,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>866775</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -354,13 +366,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1276350</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>1190625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -397,13 +409,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1076325</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1143000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -440,13 +452,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1238250</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>1181100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -483,13 +495,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1276350</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>1190625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -526,13 +538,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>1076325</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -569,13 +581,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1304925</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>1209675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -612,13 +624,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1143000</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>1171575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -655,13 +667,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1076325</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -698,13 +710,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1104900</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>1143000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -741,13 +753,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1247775</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>1171575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -784,13 +796,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1257300</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>1162050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -827,13 +839,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>1133475</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -870,13 +882,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1209675</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>1143000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -913,13 +925,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1171575</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>1171575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -956,13 +968,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1238250</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>1209675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -994,6 +1006,50 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>219076</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1038226</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1117252</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Imagen 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDA7E954-3C59-67B4-575E-5F2D67B18D2D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1743076" y="800100"/>
+          <a:ext cx="819150" cy="1002952"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
@@ -1318,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{296D561E-98EB-4F08-A3AB-6ABAB46810FA}">
-  <dimension ref="A2:M610"/>
+  <dimension ref="A2:M611"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11.42578125" customWidth="1"/>
@@ -1389,266 +1445,247 @@
     </row>
     <row r="4" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>17</v>
+        <v>202</v>
       </c>
       <c r="B4" s="5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C4" s="6"/>
-      <c r="D4" s="7">
-        <v>50.75</v>
-      </c>
-      <c r="E4" s="8">
-        <v>2.34</v>
-      </c>
-      <c r="F4" s="9">
-        <v>0.64</v>
-      </c>
-      <c r="G4" s="10">
-        <f>D4+E4+F4</f>
-        <v>53.730000000000004</v>
-      </c>
-      <c r="H4" s="9">
-        <f>G4*8</f>
-        <v>429.84000000000003</v>
-      </c>
-      <c r="I4" s="9">
-        <f>H4/0.95</f>
-        <v>452.46315789473692</v>
-      </c>
-      <c r="J4" s="9">
-        <f>(I4*2)+5</f>
-        <v>909.92631578947385</v>
-      </c>
-      <c r="K4" s="9">
-        <v>910</v>
-      </c>
+      <c r="D4" s="14">
+        <v>9.33</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
       <c r="L4" s="11">
-        <f>K4+10</f>
-        <v>920</v>
+        <v>235</v>
       </c>
       <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="5">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="7">
-        <v>19.86</v>
+        <v>50.75</v>
       </c>
       <c r="E5" s="8">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="F5" s="9">
-        <v>0.57999999999999996</v>
+        <v>0.64</v>
       </c>
       <c r="G5" s="10">
-        <f>D5+E5+F5</f>
-        <v>22.54</v>
+        <f t="shared" ref="G5:G21" si="0">D5+E5+F5</f>
+        <v>53.730000000000004</v>
       </c>
       <c r="H5" s="9">
-        <f>G5*8</f>
-        <v>180.32</v>
+        <f t="shared" ref="H4:H21" si="1">G5*8</f>
+        <v>429.84000000000003</v>
       </c>
       <c r="I5" s="9">
-        <f>H5/0.95</f>
-        <v>189.81052631578947</v>
+        <f t="shared" ref="I4:I21" si="2">H5/0.95</f>
+        <v>452.46315789473692</v>
       </c>
       <c r="J5" s="9">
-        <f>(I5*2)+5</f>
-        <v>384.62105263157895</v>
+        <f t="shared" ref="J4:J21" si="3">(I5*2)+5</f>
+        <v>909.92631578947385</v>
       </c>
       <c r="K5" s="9">
-        <v>385</v>
+        <v>910</v>
       </c>
       <c r="L5" s="11">
-        <f>K5+10</f>
-        <v>395</v>
+        <f t="shared" ref="L4:L21" si="4">K5+10</f>
+        <v>920</v>
       </c>
       <c r="M5" s="12"/>
     </row>
     <row r="6" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="5">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="7">
-        <v>12.5</v>
+        <v>19.86</v>
       </c>
       <c r="E6" s="8">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="F6" s="9">
-        <v>0.53</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="G6" s="10">
-        <f>D6+E6+F6</f>
-        <v>14.93</v>
+        <f t="shared" si="0"/>
+        <v>22.54</v>
       </c>
       <c r="H6" s="9">
-        <f>G6*8</f>
-        <v>119.44</v>
+        <f t="shared" si="1"/>
+        <v>180.32</v>
       </c>
       <c r="I6" s="9">
-        <f>H6/0.95</f>
-        <v>125.72631578947369</v>
+        <f t="shared" si="2"/>
+        <v>189.81052631578947</v>
       </c>
       <c r="J6" s="9">
-        <f>(I6*2)+5</f>
-        <v>256.45263157894738</v>
+        <f t="shared" si="3"/>
+        <v>384.62105263157895</v>
       </c>
       <c r="K6" s="9">
-        <v>260</v>
+        <v>385</v>
       </c>
       <c r="L6" s="11">
-        <f>K6+10</f>
-        <v>270</v>
+        <f t="shared" si="4"/>
+        <v>395</v>
       </c>
       <c r="M6" s="12"/>
     </row>
     <row r="7" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="7">
-        <v>5.15</v>
+        <v>12.5</v>
       </c>
       <c r="E7" s="8">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="F7" s="9">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="G7" s="10">
-        <f>D7+E7+F7</f>
-        <v>6.0400000000000009</v>
+        <f t="shared" si="0"/>
+        <v>14.93</v>
       </c>
       <c r="H7" s="9">
-        <f>G7*8</f>
-        <v>48.320000000000007</v>
+        <f t="shared" si="1"/>
+        <v>119.44</v>
       </c>
       <c r="I7" s="9">
-        <f>H7/0.95</f>
-        <v>50.863157894736851</v>
+        <f t="shared" si="2"/>
+        <v>125.72631578947369</v>
       </c>
       <c r="J7" s="9">
-        <f>(I7*2)+5</f>
-        <v>106.7263157894737</v>
+        <f t="shared" si="3"/>
+        <v>256.45263157894738</v>
       </c>
       <c r="K7" s="9">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="L7" s="11">
-        <f>K7+10</f>
-        <v>120</v>
+        <f t="shared" si="4"/>
+        <v>270</v>
       </c>
       <c r="M7" s="12"/>
     </row>
     <row r="8" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5">
         <v>30</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="7">
-        <v>5.88</v>
+        <v>5.15</v>
       </c>
       <c r="E8" s="8">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="F8" s="9">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
       <c r="G8" s="10">
-        <f>D8+E8+F8</f>
-        <v>7.669999999999999</v>
+        <f t="shared" si="0"/>
+        <v>6.0400000000000009</v>
       </c>
       <c r="H8" s="9">
-        <f>G8*8</f>
-        <v>61.359999999999992</v>
+        <f t="shared" si="1"/>
+        <v>48.320000000000007</v>
       </c>
       <c r="I8" s="9">
-        <f>H8/0.95</f>
-        <v>64.589473684210517</v>
+        <f t="shared" si="2"/>
+        <v>50.863157894736851</v>
       </c>
       <c r="J8" s="9">
-        <f>(I8*2)+5</f>
-        <v>134.17894736842103</v>
+        <f t="shared" si="3"/>
+        <v>106.7263157894737</v>
       </c>
       <c r="K8" s="9">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L8" s="11">
-        <f>K8+10</f>
-        <v>145</v>
+        <f t="shared" si="4"/>
+        <v>120</v>
       </c>
       <c r="M8" s="12"/>
     </row>
     <row r="9" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="7">
-        <v>5.15</v>
+        <v>5.88</v>
       </c>
       <c r="E9" s="8">
-        <v>0.93</v>
+        <v>1.4</v>
       </c>
       <c r="F9" s="9">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="G9" s="10">
-        <f>D9+E9+F9</f>
-        <v>6.34</v>
+        <f t="shared" si="0"/>
+        <v>7.669999999999999</v>
       </c>
       <c r="H9" s="9">
-        <f>G9*8</f>
-        <v>50.72</v>
+        <f t="shared" si="1"/>
+        <v>61.359999999999992</v>
       </c>
       <c r="I9" s="9">
-        <f>H9/0.95</f>
-        <v>53.389473684210529</v>
+        <f t="shared" si="2"/>
+        <v>64.589473684210517</v>
       </c>
       <c r="J9" s="9">
-        <f>(I9*2)+5</f>
-        <v>111.77894736842106</v>
+        <f t="shared" si="3"/>
+        <v>134.17894736842103</v>
       </c>
       <c r="K9" s="9">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="L9" s="11">
-        <f>K9+10</f>
-        <v>125</v>
+        <f t="shared" si="4"/>
+        <v>145</v>
       </c>
       <c r="M9" s="12"/>
     </row>
     <row r="10" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="5">
         <v>20</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="7">
-        <v>4.71</v>
+        <v>5.15</v>
       </c>
       <c r="E10" s="8">
         <v>0.93</v>
@@ -1657,40 +1694,40 @@
         <v>0.26</v>
       </c>
       <c r="G10" s="10">
-        <f>D10+E10+F10</f>
-        <v>5.8999999999999995</v>
+        <f t="shared" si="0"/>
+        <v>6.34</v>
       </c>
       <c r="H10" s="9">
-        <f>G10*8</f>
-        <v>47.199999999999996</v>
+        <f t="shared" si="1"/>
+        <v>50.72</v>
       </c>
       <c r="I10" s="9">
-        <f>H10/0.95</f>
-        <v>49.684210526315788</v>
+        <f t="shared" si="2"/>
+        <v>53.389473684210529</v>
       </c>
       <c r="J10" s="9">
-        <f>(I10*2)+5</f>
-        <v>104.36842105263158</v>
+        <f t="shared" si="3"/>
+        <v>111.77894736842106</v>
       </c>
       <c r="K10" s="9">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="L10" s="11">
-        <f>K10+10</f>
-        <v>115</v>
+        <f t="shared" si="4"/>
+        <v>125</v>
       </c>
       <c r="M10" s="12"/>
     </row>
     <row r="11" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="5">
         <v>20</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="7">
-        <v>5.15</v>
+        <v>4.71</v>
       </c>
       <c r="E11" s="8">
         <v>0.93</v>
@@ -1699,82 +1736,82 @@
         <v>0.26</v>
       </c>
       <c r="G11" s="10">
-        <f>D11+E11+F11</f>
-        <v>6.34</v>
+        <f t="shared" si="0"/>
+        <v>5.8999999999999995</v>
       </c>
       <c r="H11" s="9">
-        <f>G11*8</f>
-        <v>50.72</v>
+        <f t="shared" si="1"/>
+        <v>47.199999999999996</v>
       </c>
       <c r="I11" s="9">
-        <f>H11/0.95</f>
-        <v>53.389473684210529</v>
+        <f t="shared" si="2"/>
+        <v>49.684210526315788</v>
       </c>
       <c r="J11" s="9">
-        <f>(I11*2)+5</f>
-        <v>111.77894736842106</v>
+        <f t="shared" si="3"/>
+        <v>104.36842105263158</v>
       </c>
       <c r="K11" s="9">
+        <v>105</v>
+      </c>
+      <c r="L11" s="11">
+        <f t="shared" si="4"/>
         <v>115</v>
-      </c>
-      <c r="L11" s="11">
-        <f>K11+10</f>
-        <v>125</v>
       </c>
       <c r="M11" s="12"/>
     </row>
     <row r="12" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="7">
-        <v>7.36</v>
+        <v>5.15</v>
       </c>
       <c r="E12" s="8">
-        <v>1.4</v>
+        <v>0.93</v>
       </c>
       <c r="F12" s="9">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="G12" s="10">
-        <f>D12+E12+F12</f>
-        <v>9.15</v>
+        <f t="shared" si="0"/>
+        <v>6.34</v>
       </c>
       <c r="H12" s="9">
-        <f>G12*8</f>
-        <v>73.2</v>
+        <f t="shared" si="1"/>
+        <v>50.72</v>
       </c>
       <c r="I12" s="9">
-        <f>H12/0.95</f>
-        <v>77.05263157894737</v>
+        <f t="shared" si="2"/>
+        <v>53.389473684210529</v>
       </c>
       <c r="J12" s="9">
-        <f>(I12*2)+5</f>
-        <v>159.10526315789474</v>
+        <f t="shared" si="3"/>
+        <v>111.77894736842106</v>
       </c>
       <c r="K12" s="9">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="L12" s="11">
-        <f>K12+10</f>
-        <v>170</v>
+        <f t="shared" si="4"/>
+        <v>125</v>
       </c>
       <c r="M12" s="12"/>
     </row>
     <row r="13" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="5">
         <v>30</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="7">
-        <v>14.71</v>
+        <v>7.36</v>
       </c>
       <c r="E13" s="8">
         <v>1.4</v>
@@ -1783,33 +1820,33 @@
         <v>0.39</v>
       </c>
       <c r="G13" s="10">
-        <f>D13+E13+F13</f>
-        <v>16.5</v>
+        <f t="shared" si="0"/>
+        <v>9.15</v>
       </c>
       <c r="H13" s="9">
-        <f>G13*8</f>
-        <v>132</v>
+        <f t="shared" si="1"/>
+        <v>73.2</v>
       </c>
       <c r="I13" s="9">
-        <f>H13/0.95</f>
-        <v>138.94736842105263</v>
+        <f t="shared" si="2"/>
+        <v>77.05263157894737</v>
       </c>
       <c r="J13" s="9">
-        <f>(I13*2)+5</f>
-        <v>282.89473684210526</v>
+        <f t="shared" si="3"/>
+        <v>159.10526315789474</v>
       </c>
       <c r="K13" s="9">
-        <v>285</v>
+        <v>160</v>
       </c>
       <c r="L13" s="11">
-        <f>K13+10</f>
-        <v>295</v>
+        <f t="shared" si="4"/>
+        <v>170</v>
       </c>
       <c r="M13" s="12"/>
     </row>
     <row r="14" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="5">
         <v>30</v>
@@ -1825,40 +1862,40 @@
         <v>0.39</v>
       </c>
       <c r="G14" s="10">
-        <f>D14+E14+F14</f>
+        <f t="shared" si="0"/>
         <v>16.5</v>
       </c>
       <c r="H14" s="9">
-        <f>G14*8</f>
+        <f t="shared" si="1"/>
         <v>132</v>
       </c>
       <c r="I14" s="9">
-        <f>H14/0.95</f>
+        <f t="shared" si="2"/>
         <v>138.94736842105263</v>
       </c>
       <c r="J14" s="9">
-        <f>(I14*2)+5</f>
+        <f t="shared" si="3"/>
         <v>282.89473684210526</v>
       </c>
       <c r="K14" s="9">
         <v>285</v>
       </c>
       <c r="L14" s="11">
-        <f>K14+10</f>
+        <f t="shared" si="4"/>
         <v>295</v>
       </c>
       <c r="M14" s="12"/>
     </row>
     <row r="15" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15" s="5">
         <v>30</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="7">
-        <v>15.45</v>
+        <v>14.71</v>
       </c>
       <c r="E15" s="8">
         <v>1.4</v>
@@ -1867,208 +1904,208 @@
         <v>0.39</v>
       </c>
       <c r="G15" s="10">
-        <f>D15+E15+F15</f>
-        <v>17.239999999999998</v>
+        <f t="shared" si="0"/>
+        <v>16.5</v>
       </c>
       <c r="H15" s="9">
-        <f>G15*8</f>
-        <v>137.91999999999999</v>
+        <f t="shared" si="1"/>
+        <v>132</v>
       </c>
       <c r="I15" s="9">
-        <f>H15/0.95</f>
-        <v>145.17894736842103</v>
+        <f t="shared" si="2"/>
+        <v>138.94736842105263</v>
       </c>
       <c r="J15" s="9">
-        <f>(I15*2)+5</f>
-        <v>295.35789473684207</v>
+        <f t="shared" si="3"/>
+        <v>282.89473684210526</v>
       </c>
       <c r="K15" s="9">
+        <v>285</v>
+      </c>
+      <c r="L15" s="11">
+        <f t="shared" si="4"/>
         <v>295</v>
-      </c>
-      <c r="L15" s="11">
-        <f>K15+10</f>
-        <v>305</v>
       </c>
       <c r="M15" s="12"/>
     </row>
     <row r="16" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="7">
-        <v>20.59</v>
+        <v>15.45</v>
       </c>
       <c r="E16" s="8">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="F16" s="9">
-        <v>0.53</v>
+        <v>0.39</v>
       </c>
       <c r="G16" s="10">
-        <f>D16+E16+F16</f>
-        <v>23.02</v>
+        <f t="shared" si="0"/>
+        <v>17.239999999999998</v>
       </c>
       <c r="H16" s="9">
-        <f>G16*8</f>
-        <v>184.16</v>
+        <f t="shared" si="1"/>
+        <v>137.91999999999999</v>
       </c>
       <c r="I16" s="9">
-        <f>H16/0.95</f>
-        <v>193.85263157894738</v>
+        <f t="shared" si="2"/>
+        <v>145.17894736842103</v>
       </c>
       <c r="J16" s="9">
-        <f>(I16*2)+5</f>
-        <v>392.70526315789476</v>
+        <f t="shared" si="3"/>
+        <v>295.35789473684207</v>
       </c>
       <c r="K16" s="9">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="L16" s="11">
-        <f>K16+10</f>
-        <v>405</v>
+        <f t="shared" si="4"/>
+        <v>305</v>
       </c>
       <c r="M16" s="12"/>
     </row>
     <row r="17" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B17" s="5">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="7">
-        <v>4.41</v>
+        <v>20.59</v>
       </c>
       <c r="E17" s="8">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="F17" s="9">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="G17" s="10">
-        <f>D17+E17+F17</f>
-        <v>5.3000000000000007</v>
+        <f t="shared" si="0"/>
+        <v>23.02</v>
       </c>
       <c r="H17" s="9">
-        <f>G17*8</f>
-        <v>42.400000000000006</v>
+        <f t="shared" si="1"/>
+        <v>184.16</v>
       </c>
       <c r="I17" s="9">
-        <f>H17/0.95</f>
-        <v>44.631578947368432</v>
+        <f t="shared" si="2"/>
+        <v>193.85263157894738</v>
       </c>
       <c r="J17" s="9">
-        <f>(I17*2)+5</f>
-        <v>94.263157894736864</v>
+        <f t="shared" si="3"/>
+        <v>392.70526315789476</v>
       </c>
       <c r="K17" s="9">
-        <v>95</v>
+        <v>395</v>
       </c>
       <c r="L17" s="11">
-        <f>K17+10</f>
-        <v>105</v>
+        <f t="shared" si="4"/>
+        <v>405</v>
       </c>
       <c r="M17" s="12"/>
     </row>
     <row r="18" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="7">
-        <v>6.62</v>
+        <v>4.41</v>
       </c>
       <c r="E18" s="8">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="F18" s="9">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
       <c r="G18" s="10">
-        <f>D18+E18+F18</f>
-        <v>8.41</v>
+        <f t="shared" si="0"/>
+        <v>5.3000000000000007</v>
       </c>
       <c r="H18" s="9">
-        <f>G18*8</f>
-        <v>67.28</v>
+        <f t="shared" si="1"/>
+        <v>42.400000000000006</v>
       </c>
       <c r="I18" s="9">
-        <f>H18/0.95</f>
-        <v>70.821052631578951</v>
+        <f t="shared" si="2"/>
+        <v>44.631578947368432</v>
       </c>
       <c r="J18" s="9">
-        <f>(I18*2)+5</f>
-        <v>146.6421052631579</v>
+        <f t="shared" si="3"/>
+        <v>94.263157894736864</v>
       </c>
       <c r="K18" s="9">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="L18" s="11">
-        <f>K18+10</f>
-        <v>160</v>
+        <f t="shared" si="4"/>
+        <v>105</v>
       </c>
       <c r="M18" s="12"/>
     </row>
     <row r="19" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" s="5">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="7">
-        <v>7.36</v>
+        <v>6.62</v>
       </c>
       <c r="E19" s="8">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="F19" s="9">
-        <v>0.19</v>
+        <v>0.39</v>
       </c>
       <c r="G19" s="10">
-        <f>D19+E19+F19</f>
-        <v>8.25</v>
+        <f t="shared" si="0"/>
+        <v>8.41</v>
       </c>
       <c r="H19" s="9">
-        <f>G19*8</f>
-        <v>66</v>
+        <f t="shared" si="1"/>
+        <v>67.28</v>
       </c>
       <c r="I19" s="9">
-        <f>H19/0.95</f>
-        <v>69.473684210526315</v>
+        <f t="shared" si="2"/>
+        <v>70.821052631578951</v>
       </c>
       <c r="J19" s="9">
-        <f>(I19*2)+5</f>
-        <v>143.94736842105263</v>
+        <f t="shared" si="3"/>
+        <v>146.6421052631579</v>
       </c>
       <c r="K19" s="9">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="L19" s="11">
-        <f>K19+10</f>
-        <v>155</v>
+        <f t="shared" si="4"/>
+        <v>160</v>
       </c>
       <c r="M19" s="12"/>
     </row>
     <row r="20" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" s="5">
         <v>15</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="7">
-        <v>4.41</v>
+        <v>7.36</v>
       </c>
       <c r="E20" s="8">
         <v>0.7</v>
@@ -2077,31 +2114,72 @@
         <v>0.19</v>
       </c>
       <c r="G20" s="10">
-        <f>D20+E20+F20</f>
-        <v>5.3000000000000007</v>
+        <f t="shared" si="0"/>
+        <v>8.25</v>
       </c>
       <c r="H20" s="9">
-        <f>G20*8</f>
-        <v>42.400000000000006</v>
+        <f t="shared" si="1"/>
+        <v>66</v>
       </c>
       <c r="I20" s="9">
-        <f>H20/0.95</f>
-        <v>44.631578947368432</v>
+        <f t="shared" si="2"/>
+        <v>69.473684210526315</v>
       </c>
       <c r="J20" s="9">
-        <f>(I20*2)+5</f>
-        <v>94.263157894736864</v>
+        <f t="shared" si="3"/>
+        <v>143.94736842105263</v>
       </c>
       <c r="K20" s="9">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="L20" s="11">
-        <f>K20+10</f>
-        <v>105</v>
+        <f t="shared" si="4"/>
+        <v>155</v>
       </c>
       <c r="M20" s="12"/>
     </row>
-    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>1</v>
+      </c>
+      <c r="B21" s="5">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="7">
+        <v>4.41</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="F21" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="G21" s="10">
+        <f t="shared" si="0"/>
+        <v>5.3000000000000007</v>
+      </c>
+      <c r="H21" s="9">
+        <f t="shared" si="1"/>
+        <v>42.400000000000006</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="2"/>
+        <v>44.631578947368432</v>
+      </c>
+      <c r="J21" s="9">
+        <f t="shared" si="3"/>
+        <v>94.263157894736864</v>
+      </c>
+      <c r="K21" s="9">
+        <v>95</v>
+      </c>
+      <c r="L21" s="11">
+        <f t="shared" si="4"/>
+        <v>105</v>
+      </c>
+      <c r="M21" s="12"/>
+    </row>
     <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2691,32 +2769,34 @@
     <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:L20">
-    <sortCondition descending="1" ref="A3:A20"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:L21">
+    <sortCondition descending="1" ref="A3:A21"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D20" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{69986E4C-0663-4546-BC83-B8C9CA1D9714}"/>
-    <hyperlink ref="D19" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{955C1DB4-1507-487D-9C08-C5373BA80E25}"/>
-    <hyperlink ref="D18" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7C769044-B74D-4DB0-A432-F0604E52B7B1}"/>
-    <hyperlink ref="D17" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5A5F7E90-E8F2-4EF8-A252-175AA9D8E749}"/>
-    <hyperlink ref="D16" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{42ECB438-6F40-416D-AF89-624A89CEB4E6}"/>
-    <hyperlink ref="D15" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{B803DBFB-BFB9-4C8B-A29F-F9FBA9C59485}"/>
-    <hyperlink ref="D14" r:id="rId7" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{D7A2E6E0-86F4-41AF-9E23-CBA761343744}"/>
-    <hyperlink ref="D13" r:id="rId8" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{C81E99B9-57B1-403E-8702-79973F98CF07}"/>
-    <hyperlink ref="D12" r:id="rId9" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{817B4711-C658-4E5E-AD69-E367C713B93E}"/>
-    <hyperlink ref="D11" r:id="rId10" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{8007FD0A-DEC7-4391-AD1E-C9D3683C3C75}"/>
-    <hyperlink ref="D10" r:id="rId11" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{F9115F14-6FBC-4F8F-9604-F543031CE620}"/>
-    <hyperlink ref="D9" r:id="rId12" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2737C18A-F777-48EB-BA87-39017E7C8A1E}"/>
-    <hyperlink ref="D8" r:id="rId13" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{12F4E592-5438-4BED-B7E2-344ACBEC7F96}"/>
-    <hyperlink ref="D7" r:id="rId14" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{DCDC800C-99D0-4E42-A41E-D41CB6F4B5D4}"/>
-    <hyperlink ref="D6" r:id="rId15" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5435EF40-401F-4600-B962-E44BD15563E6}"/>
-    <hyperlink ref="D5" r:id="rId16" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{B7CF205F-A295-4EA9-879B-6BDA2A7260AB}"/>
-    <hyperlink ref="D4" r:id="rId17" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7D2CABEC-E20E-4018-BA6C-BA3A1628B1EA}"/>
+    <hyperlink ref="D21" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{69986E4C-0663-4546-BC83-B8C9CA1D9714}"/>
+    <hyperlink ref="D20" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{955C1DB4-1507-487D-9C08-C5373BA80E25}"/>
+    <hyperlink ref="D19" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7C769044-B74D-4DB0-A432-F0604E52B7B1}"/>
+    <hyperlink ref="D18" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5A5F7E90-E8F2-4EF8-A252-175AA9D8E749}"/>
+    <hyperlink ref="D17" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{42ECB438-6F40-416D-AF89-624A89CEB4E6}"/>
+    <hyperlink ref="D16" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{B803DBFB-BFB9-4C8B-A29F-F9FBA9C59485}"/>
+    <hyperlink ref="D15" r:id="rId7" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{D7A2E6E0-86F4-41AF-9E23-CBA761343744}"/>
+    <hyperlink ref="D14" r:id="rId8" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{C81E99B9-57B1-403E-8702-79973F98CF07}"/>
+    <hyperlink ref="D13" r:id="rId9" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{817B4711-C658-4E5E-AD69-E367C713B93E}"/>
+    <hyperlink ref="D12" r:id="rId10" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{8007FD0A-DEC7-4391-AD1E-C9D3683C3C75}"/>
+    <hyperlink ref="D11" r:id="rId11" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{F9115F14-6FBC-4F8F-9604-F543031CE620}"/>
+    <hyperlink ref="D10" r:id="rId12" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2737C18A-F777-48EB-BA87-39017E7C8A1E}"/>
+    <hyperlink ref="D9" r:id="rId13" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{12F4E592-5438-4BED-B7E2-344ACBEC7F96}"/>
+    <hyperlink ref="D8" r:id="rId14" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{DCDC800C-99D0-4E42-A41E-D41CB6F4B5D4}"/>
+    <hyperlink ref="D7" r:id="rId15" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{5435EF40-401F-4600-B962-E44BD15563E6}"/>
+    <hyperlink ref="D6" r:id="rId16" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{B7CF205F-A295-4EA9-879B-6BDA2A7260AB}"/>
+    <hyperlink ref="D5" r:id="rId17" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{7D2CABEC-E20E-4018-BA6C-BA3A1628B1EA}"/>
+    <hyperlink ref="D4" r:id="rId18" display="https://detail.1688.com/offer/1002175660973.html" xr:uid="{384647D0-5E31-4E1A-AF96-09805A8506CC}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId18"/>
-  <drawing r:id="rId19"/>
+  <pageSetup orientation="portrait" r:id="rId19"/>
+  <drawing r:id="rId20"/>
 </worksheet>
 </file>
--- a/COLLARES SWA.xlsx
+++ b/COLLARES SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A636A673-8C85-4281-BAFA-BE356296C673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F92F15-42C5-408B-B770-632ECBB43BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{858CB977-914C-4BFC-86E4-E9C9E95983A5}"/>
   </bookViews>
@@ -1488,22 +1488,22 @@
         <v>53.730000000000004</v>
       </c>
       <c r="H5" s="9">
-        <f t="shared" ref="H4:H21" si="1">G5*8</f>
+        <f t="shared" ref="H5:H21" si="1">G5*8</f>
         <v>429.84000000000003</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" ref="I4:I21" si="2">H5/0.95</f>
+        <f t="shared" ref="I5:I21" si="2">H5/0.95</f>
         <v>452.46315789473692</v>
       </c>
       <c r="J5" s="9">
-        <f t="shared" ref="J4:J21" si="3">(I5*2)+5</f>
+        <f t="shared" ref="J5:J21" si="3">(I5*2)+5</f>
         <v>909.92631578947385</v>
       </c>
       <c r="K5" s="9">
         <v>910</v>
       </c>
       <c r="L5" s="11">
-        <f t="shared" ref="L4:L21" si="4">K5+10</f>
+        <f t="shared" ref="L5:L21" si="4">K5+10</f>
         <v>920</v>
       </c>
       <c r="M5" s="12"/>
